--- a/结果/1.识别结果/【人教版】一年级下册(2025春版)道德与法治电子课本_人头计数.xlsx
+++ b/结果/1.识别结果/【人教版】一年级下册(2025春版)道德与法治电子课本_人头计数.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -9606,7 +9606,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -14496,7 +14496,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>户外</t>
+          <t>公共场所</t>
         </is>
       </c>
     </row>
